--- a/real_estate_forms/011_todays_mortgage_rates--real_estate_forms.xlsx
+++ b/real_estate_forms/011_todays_mortgage_rates--real_estate_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -1165,29 +1165,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5/1_arm</t>
+          <t>7/1_arm</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>5/1 ARM</t>
+          <t>7/1 ARM</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>loan_type_choices</t>
+          <t>income_type_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7/1_arm</t>
+          <t>single</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>7/1 ARM</t>
+          <t>Single</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>single</t>
+          <t>married</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Married</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>married</t>
+          <t>separated</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Married</t>
+          <t>Separated</t>
         </is>
       </c>
     </row>
@@ -1233,29 +1233,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>separated</t>
+          <t>divorced</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Separated</t>
+          <t>Divorced</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>income_type_choices</t>
+          <t>mortgage_rate_type_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>divorced</t>
+          <t>fixed</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Divorced</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -1267,29 +1267,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>fixed</t>
+          <t>adjustable</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Adjustable</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mortgage_rate_type_choices</t>
+          <t>property_type_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>adjustable</t>
+          <t>primary_residence</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Adjustable</t>
+          <t>Primary Residence</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>primary_residence</t>
+          <t>investment</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Primary Residence</t>
+          <t>Investment</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>investment</t>
+          <t>vacation_home</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Investment</t>
+          <t>Vacation Home</t>
         </is>
       </c>
     </row>
@@ -1335,29 +1335,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>vacation_home</t>
+          <t>second_home</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vacation Home</t>
+          <t>Second Home</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>property_type_choices</t>
+          <t>employment_status_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>second_home</t>
+          <t>employed</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Second Home</t>
+          <t>Employed</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>employed</t>
+          <t>self-employed</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Employed</t>
+          <t>Self-Employed</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>self-employed</t>
+          <t>retired</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Self-Employed</t>
+          <t>Retired</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>retired</t>
+          <t>disabled</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Retired</t>
+          <t>Disabled</t>
         </is>
       </c>
     </row>
@@ -1420,29 +1420,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>disabled</t>
+          <t>unemployed</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Disabled</t>
+          <t>Unemployed</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>employment_status_choices</t>
+          <t>income_frequency_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>unemployed</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Unemployed</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -1471,29 +1471,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Annually</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>income_frequency_choices</t>
+          <t>annual_income_frequency_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>annually</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Annually</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -1522,29 +1522,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Annually</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>annual_income_frequency_choices</t>
+          <t>income_source_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>annually</t>
+          <t>business</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Annually</t>
+          <t>Business</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>business</t>
+          <t>salary</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Salary</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>salary</t>
+          <t>investment</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Salary</t>
+          <t>Investment</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>investment</t>
+          <t>self-employed</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Investment</t>
+          <t>Self-Employed</t>
         </is>
       </c>
     </row>
@@ -1607,29 +1607,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>self-employed</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Self-Employed</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>income_source_choices</t>
+          <t>loan_purpose_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>purchase</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Purchase</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>purchase</t>
+          <t>refinance</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Purchase</t>
+          <t>Refinance</t>
         </is>
       </c>
     </row>
@@ -1658,29 +1658,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>refinance</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Refinance</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>loan_purpose_choices</t>
+          <t>credit_history_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>excellent</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1726,29 +1726,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>credit_history_choices</t>
+          <t>employment_duration_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>poor</t>
+          <t>less_than_2_years</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Less Than 2 Years</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>less_than_2_years</t>
+          <t>2-5_years</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Less Than 2 Years</t>
+          <t>2-5 Years</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2-5_years</t>
+          <t>5-10_years</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2-5 Years</t>
+          <t>5-10 Years</t>
         </is>
       </c>
     </row>
@@ -1794,27 +1794,10 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5-10_years</t>
+          <t>more_than_10_years</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
-        <is>
-          <t>5-10 Years</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>employment_duration_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>more_than_10_years</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
         <is>
           <t>More Than 10 Years</t>
         </is>
